--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N43_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.18816228617074</v>
+        <v>4.418076371502746</v>
       </c>
       <c r="D2" t="n">
-        <v>8.037753275905734</v>
+        <v>1.306134907334682</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
